--- a/static/Resign_template.xlsx
+++ b/static/Resign_template.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\MPR-vg-ifm\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5326FAA9-4D84-4D74-B25E-FA79C0DCDFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4610CD87-5A6B-48CB-AEC6-E3C942462DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="9825" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15750" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MK" sheetId="3" r:id="rId1"/>
+    <sheet name="TEMPLATE" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>STT</t>
   </si>
@@ -60,6 +60,9 @@
       </rPr>
       <t>廠離職人員名單</t>
     </r>
+  </si>
+  <si>
+    <t>POSITION</t>
   </si>
 </sst>
 </file>
@@ -444,18 +447,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="7" customWidth="1"/>
     <col min="2" max="2" width="12.140625" style="8" customWidth="1"/>
     <col min="3" max="3" width="39.140625" style="7" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="40.85546875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="9" customWidth="1"/>
+    <col min="5" max="6" width="40.85546875" style="10" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>6</v>
       </c>
@@ -464,8 +467,9 @@
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G1" s="11"/>
+    </row>
+    <row r="2" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,148 +486,168 @@
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="5"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F4" s="5"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="5"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F6" s="5"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="4"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="5"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F9" s="5"/>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="5"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F11" s="5"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="5"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="4"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F13" s="5"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="5"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="4"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F16" s="5"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="4"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F18" s="5"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="4"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/static/Resign_template.xlsx
+++ b/static/Resign_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\MPR-vg-ifm\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chung.vo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4610CD87-5A6B-48CB-AEC6-E3C942462DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10433E86-7621-4844-8251-6679A5F3A607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15750" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TEMPLATE" sheetId="3" r:id="rId1"/>
@@ -27,42 +27,36 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>EMPNO</t>
-  </si>
-  <si>
-    <t>NAME_S</t>
-  </si>
-  <si>
-    <t>DEPT_NO</t>
-  </si>
-  <si>
-    <t>DEPT NAME</t>
-  </si>
-  <si>
-    <t>DIMISION DATE</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">DANH SÁCH CÔNG NHÂN THÔI VIỆC XƯỞNG
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>廠離職人員名單</t>
-    </r>
-  </si>
-  <si>
-    <t>POSITION</t>
+    <t>STT
+NO.</t>
+  </si>
+  <si>
+    <t>Số thẻ CNV
+EMPNO</t>
+  </si>
+  <si>
+    <t>Họ tên
+NAME_S</t>
+  </si>
+  <si>
+    <t>Mã Bộ phận
+DEPT_NO</t>
+  </si>
+  <si>
+    <t>Tên Bộ phận
+DEPT NAME</t>
+  </si>
+  <si>
+    <t>Vị trí
+POSITION</t>
+  </si>
+  <si>
+    <t>Ngày thôi việc
+RESIGNATION DATE</t>
+  </si>
+  <si>
+    <t>DANH SÁCH CÔNG NHÂN VIÊN THÔI VIỆC
+LIST OF RESIGNED EMPLOYEES</t>
   </si>
 </sst>
 </file>
@@ -72,26 +66,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -109,6 +87,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -152,22 +137,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -180,7 +165,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -451,16 +436,16 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="8" customWidth="1"/>
     <col min="3" max="3" width="39.140625" style="7" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" style="9" customWidth="1"/>
     <col min="5" max="6" width="40.85546875" style="10" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="26.85546875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -486,10 +471,10 @@
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
